--- a/data/teaching.xlsx
+++ b/data/teaching.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/conorisco/Dropbox (Personal)/Jobs/CV and Publications/CV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE7751C-6119-AF44-B5C8-1A348588504C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38E376C6-8EAE-424C-9F6E-4B5CE584F0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4240" yWindow="2980" windowWidth="25680" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6220" yWindow="3400" windowWidth="36880" windowHeight="21060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="54">
   <si>
     <t>with</t>
   </si>
@@ -181,6 +181,12 @@
   </si>
   <si>
     <t>12 Members</t>
+  </si>
+  <si>
+    <t>Intro to data science</t>
+  </si>
+  <si>
+    <t>MSc Healthcare Infection</t>
   </si>
 </sst>
 </file>
@@ -522,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="78.83203125" customWidth="1"/>
@@ -809,6 +815,20 @@
         <v>51</v>
       </c>
     </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18">
+        <v>2026</v>
+      </c>
+      <c r="D18" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
